--- a/ITU/programs.xlsx
+++ b/ITU/programs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\ITU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED76E237-A04B-4E98-B60E-C285CBADBCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2621E763-5289-4C83-958D-0A1BA25610CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{C0146A36-20A1-4167-B359-2C0469CE698B}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1 (3)" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$61</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="262">
   <si>
     <t>Faculties</t>
   </si>
@@ -271,13 +272,571 @@
   </si>
   <si>
     <t>ITU-TRNCIndustrial Engineering (%100 English) (Paid)</t>
+  </si>
+  <si>
+    <t>$160,000 to $200,000</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>$110,000 to $140,000</t>
+  </si>
+  <si>
+    <t>$130,000 to $180,000</t>
+  </si>
+  <si>
+    <t>$150,000 to $200,000</t>
+  </si>
+  <si>
+    <t>General Chemistry I</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>BIL 110E</t>
+  </si>
+  <si>
+    <t>Introduction to Program Language (C)</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>MAT 103E</t>
+  </si>
+  <si>
+    <t>Mathematics I</t>
+  </si>
+  <si>
+    <t>FIZ 101E</t>
+  </si>
+  <si>
+    <t>Physics I</t>
+  </si>
+  <si>
+    <t>FIZ 101EL</t>
+  </si>
+  <si>
+    <t>Physics I Laboratory</t>
+  </si>
+  <si>
+    <t>UZB 112E</t>
+  </si>
+  <si>
+    <t>Computer Aided Drafting</t>
+  </si>
+  <si>
+    <t>ING 100</t>
+  </si>
+  <si>
+    <t>EAP Through Global Goals</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>2. Semester</t>
+  </si>
+  <si>
+    <t>Course Code</t>
+  </si>
+  <si>
+    <t>Course Title</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>Theoretical</t>
+  </si>
+  <si>
+    <t>Tutorial</t>
+  </si>
+  <si>
+    <t>Lab.</t>
+  </si>
+  <si>
+    <t>ECTS</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Compulsory/Elective</t>
+  </si>
+  <si>
+    <t>Semester</t>
+  </si>
+  <si>
+    <t>UZB 106E</t>
+  </si>
+  <si>
+    <t>Intro. to Astronaut. Eng.&amp;Des.</t>
+  </si>
+  <si>
+    <t>ED</t>
+  </si>
+  <si>
+    <t>STA 201E</t>
+  </si>
+  <si>
+    <t>Statics</t>
+  </si>
+  <si>
+    <t>MAT 104E</t>
+  </si>
+  <si>
+    <t>Mathematics II</t>
+  </si>
+  <si>
+    <t>FIZ 102E</t>
+  </si>
+  <si>
+    <t>Physics II</t>
+  </si>
+  <si>
+    <t>ING 112A</t>
+  </si>
+  <si>
+    <t>Basics of Academic Writing</t>
+  </si>
+  <si>
+    <t>FIZ 102EL</t>
+  </si>
+  <si>
+    <t>Physics II Laboratory</t>
+  </si>
+  <si>
+    <t>DAN 102</t>
+  </si>
+  <si>
+    <t>Entrepreneurship and Career Advising</t>
+  </si>
+  <si>
+    <t>MAT 261E</t>
+  </si>
+  <si>
+    <t>Linear Algebra</t>
+  </si>
+  <si>
+    <t>3. Semester</t>
+  </si>
+  <si>
+    <t>MAT 201E</t>
+  </si>
+  <si>
+    <t>Differential Equations</t>
+  </si>
+  <si>
+    <t>DNK 201E</t>
+  </si>
+  <si>
+    <t>Dynamics</t>
+  </si>
+  <si>
+    <t>MUK 211E</t>
+  </si>
+  <si>
+    <t>Strength of Materials</t>
+  </si>
+  <si>
+    <t>TUR 121</t>
+  </si>
+  <si>
+    <t>Turkish I</t>
+  </si>
+  <si>
+    <t>UCK 217E</t>
+  </si>
+  <si>
+    <t>Aerospace Materials</t>
+  </si>
+  <si>
+    <t>UCK 207E</t>
+  </si>
+  <si>
+    <t>Thermodynamics</t>
+  </si>
+  <si>
+    <t>4. Semester</t>
+  </si>
+  <si>
+    <t>AKM 219E</t>
+  </si>
+  <si>
+    <t>Fluid Mechanics</t>
+  </si>
+  <si>
+    <t>MAT 202E</t>
+  </si>
+  <si>
+    <t>Numerical Methods</t>
+  </si>
+  <si>
+    <t>TUR 122</t>
+  </si>
+  <si>
+    <t>Turkish II</t>
+  </si>
+  <si>
+    <t>UCK 203E</t>
+  </si>
+  <si>
+    <t>Circuits, Signals and Systems</t>
+  </si>
+  <si>
+    <t>UZB 337E</t>
+  </si>
+  <si>
+    <t>Aerospace Structures</t>
+  </si>
+  <si>
+    <t>ING 201A</t>
+  </si>
+  <si>
+    <t>Essentials of Research Paper Writing</t>
+  </si>
+  <si>
+    <t>UZB 220E</t>
+  </si>
+  <si>
+    <t>Mechanical Vibrations</t>
+  </si>
+  <si>
+    <t>5. Semester</t>
+  </si>
+  <si>
+    <t>UCK 305E</t>
+  </si>
+  <si>
+    <t>Aerodynamics</t>
+  </si>
+  <si>
+    <t>UZB 352E</t>
+  </si>
+  <si>
+    <t>Orbital Mechanics</t>
+  </si>
+  <si>
+    <t>UZB 301E</t>
+  </si>
+  <si>
+    <t>Measurement Techniques</t>
+  </si>
+  <si>
+    <t>UCK 303E</t>
+  </si>
+  <si>
+    <t>Automatic Control</t>
+  </si>
+  <si>
+    <t>UZB 411E</t>
+  </si>
+  <si>
+    <t>Space Environment</t>
+  </si>
+  <si>
+    <t>5th Semester Elective Courses - ITB</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>5th Semester Elective Courses</t>
+  </si>
+  <si>
+    <t>4/4.5/5/6</t>
+  </si>
+  <si>
+    <t>6. Semester</t>
+  </si>
+  <si>
+    <t>UZB 310E</t>
+  </si>
+  <si>
+    <t>Compressible Aerodynamics</t>
+  </si>
+  <si>
+    <t>UCK 304E</t>
+  </si>
+  <si>
+    <t>Experimental Engineering</t>
+  </si>
+  <si>
+    <t>UZB 421E</t>
+  </si>
+  <si>
+    <t>Attitude Determination and Control</t>
+  </si>
+  <si>
+    <t>UZB 314E</t>
+  </si>
+  <si>
+    <t>Heat Transfer</t>
+  </si>
+  <si>
+    <t>UZB 451E</t>
+  </si>
+  <si>
+    <t>Spacecraft Communications</t>
+  </si>
+  <si>
+    <t>6th Semester Elective Courses - TM</t>
+  </si>
+  <si>
+    <t>2.5/3</t>
+  </si>
+  <si>
+    <t>5/5.5</t>
+  </si>
+  <si>
+    <t>7. Semester</t>
+  </si>
+  <si>
+    <t>ATA 121</t>
+  </si>
+  <si>
+    <t>History of Turkish Revolution I</t>
+  </si>
+  <si>
+    <t>UZB 4901E</t>
+  </si>
+  <si>
+    <t>Astronautical Eng. Design I</t>
+  </si>
+  <si>
+    <t>UZB 441E</t>
+  </si>
+  <si>
+    <t>Rocket Propulsion</t>
+  </si>
+  <si>
+    <t>UZB 419E</t>
+  </si>
+  <si>
+    <t>Spacecraft Systems Design I</t>
+  </si>
+  <si>
+    <t>7th Semester Elective Courses - MT</t>
+  </si>
+  <si>
+    <t>4.5/5/7</t>
+  </si>
+  <si>
+    <t>7th Semester Elective Crs-TM</t>
+  </si>
+  <si>
+    <t>8. Semester</t>
+  </si>
+  <si>
+    <t>ATA 122</t>
+  </si>
+  <si>
+    <t>History of Turkish Revolution II</t>
+  </si>
+  <si>
+    <t>UZB 4902E</t>
+  </si>
+  <si>
+    <t>Astronautical Eng. Design II</t>
+  </si>
+  <si>
+    <t>UZB 420E</t>
+  </si>
+  <si>
+    <t>Spacecraft Systems Design II</t>
+  </si>
+  <si>
+    <t>8th Semester Elective Crse-MT</t>
+  </si>
+  <si>
+    <t>8th Semester Elective Courses I</t>
+  </si>
+  <si>
+    <t>Intro. to Electronics and Comm. Eng. and Engineering Ethics</t>
+  </si>
+  <si>
+    <t>KIM 101E</t>
+  </si>
+  <si>
+    <t>EEF 281E</t>
+  </si>
+  <si>
+    <t>Linear Algebra and Applications</t>
+  </si>
+  <si>
+    <t>EEF 110E</t>
+  </si>
+  <si>
+    <t>Intr. to Programming Language(C)</t>
+  </si>
+  <si>
+    <t>EEF 211E</t>
+  </si>
+  <si>
+    <t>Basics of Electrical Circuits</t>
+  </si>
+  <si>
+    <t>EEF 210E</t>
+  </si>
+  <si>
+    <t>EEF 205E</t>
+  </si>
+  <si>
+    <t>Introduction to Logic Design</t>
+  </si>
+  <si>
+    <t>EEF 271E</t>
+  </si>
+  <si>
+    <t>Probability and Statistics</t>
+  </si>
+  <si>
+    <t>3rd Sem. Elective Course(TB)</t>
+  </si>
+  <si>
+    <t>3rd Sem. Elective Course(TM)</t>
+  </si>
+  <si>
+    <t>EEF 232E</t>
+  </si>
+  <si>
+    <t>Circuit and System Analysis</t>
+  </si>
+  <si>
+    <t>EEF 212E</t>
+  </si>
+  <si>
+    <t>Electromagnetic Theory I</t>
+  </si>
+  <si>
+    <t>EEF 262E</t>
+  </si>
+  <si>
+    <t>Fundamentals of Electronics</t>
+  </si>
+  <si>
+    <t>EEF 206E</t>
+  </si>
+  <si>
+    <t>Signal Processing and Linear Systems</t>
+  </si>
+  <si>
+    <t>EEF 221E</t>
+  </si>
+  <si>
+    <t>Basics of Electric Circuits Lab.</t>
+  </si>
+  <si>
+    <t>4th Sem. Elective Course(TM)</t>
+  </si>
+  <si>
+    <t>4.5/5/6</t>
+  </si>
+  <si>
+    <t>EEF 311E</t>
+  </si>
+  <si>
+    <t>Numerical Analysis with Python</t>
+  </si>
+  <si>
+    <t>KON 313E</t>
+  </si>
+  <si>
+    <t>Feedback Control Systems</t>
+  </si>
+  <si>
+    <t>EHB 307E</t>
+  </si>
+  <si>
+    <t>Communication I</t>
+  </si>
+  <si>
+    <t>EHB 324E</t>
+  </si>
+  <si>
+    <t>Logic Design Lab.</t>
+  </si>
+  <si>
+    <t>5th Sem. Compulsory Elect. I (MT)</t>
+  </si>
+  <si>
+    <t>5th Sem. Compulsory Elect. II (MT)</t>
+  </si>
+  <si>
+    <t>EHB 311E</t>
+  </si>
+  <si>
+    <t>Introduction to Electronics Laboratory</t>
+  </si>
+  <si>
+    <t>6th Sem. Comp. Elect.I (MT)</t>
+  </si>
+  <si>
+    <t>6th Sem. Comp. Elect.II (MT)</t>
+  </si>
+  <si>
+    <t>6thSm.Comp.Elect.III(MT)-Design</t>
+  </si>
+  <si>
+    <t>6thSm.Comp.Elect.IV(MT)-Design</t>
+  </si>
+  <si>
+    <t>6th Semester Elct. Course(SNT)</t>
+  </si>
+  <si>
+    <t>EHB 4901E</t>
+  </si>
+  <si>
+    <t>Electronics and Communication Engineering Design I</t>
+  </si>
+  <si>
+    <t>7th Sem.Elect.Course I (MT)</t>
+  </si>
+  <si>
+    <t>7th Sem.Elect.Course II (MT)</t>
+  </si>
+  <si>
+    <t>7thSm.Elct.Crs.III(MT)-Faculty</t>
+  </si>
+  <si>
+    <t>EHB 4902E</t>
+  </si>
+  <si>
+    <t>Electronics and Communication Engeneering Design II</t>
+  </si>
+  <si>
+    <t>8th Sem.Elect.Course (ITB)</t>
+  </si>
+  <si>
+    <t>8th Sem.Elect.Course I (MT)</t>
+  </si>
+  <si>
+    <t>8thSem.Elect.CrsII (MT)Faculty</t>
+  </si>
+  <si>
+    <t>1. Semester</t>
+  </si>
+  <si>
+    <t>Astronautical Engineering Course Plan</t>
+  </si>
+  <si>
+    <t>EHB 101E</t>
+  </si>
+  <si>
+    <t>Electronics and Communication Engineering Course Plan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,8 +857,49 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3B8CEA"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF062A54"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19"/>
+      <color rgb="FF062A54"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,8 +930,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -384,11 +990,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF002867"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -405,8 +1021,46 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1932,16 +2586,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB17E8A-5151-474E-A20A-B54F6EB433A8}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.7109375" customWidth="1"/>
     <col min="2" max="2" width="111.85546875" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1951,8 +2605,11 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1962,8 +2619,11 @@
       <c r="C2" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1974,7 +2634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1985,7 +2645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1996,7 +2656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2007,7 +2667,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -2018,7 +2678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -2029,7 +2689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -2040,7 +2700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -2051,7 +2711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -2062,7 +2722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -2073,7 +2733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2084,7 +2744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -2094,8 +2754,11 @@
       <c r="C14" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -2105,8 +2768,11 @@
       <c r="C15" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
@@ -2117,7 +2783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
@@ -2128,7 +2794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
@@ -2139,7 +2805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2149,8 +2815,11 @@
       <c r="C19" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2162,26 +2831,3691 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C20" xr:uid="{B6689D0A-8653-4223-B9D9-AB23C60D1176}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Faculty of Aeronautics and Astronautics"/>
-        <filter val="Faculty of Computer and Informatics Engineering"/>
-        <filter val="Faculty of Electrical and Electronics Engineering"/>
-        <filter val="Faculty of Mines"/>
-        <filter val="Faculty of Science and Letters"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Astronautical Engineering (%100 English)"/>
-        <filter val="Electronics and Communication Engineering (%100 English)"/>
-        <filter val="Molecular Biology and Genetics (%100 English)"/>
-        <filter val="Petroleum and Natural Gas Engineering (%100 English)"/>
-        <filter val="Robotics and Autonomous Systems Engineering (%100 English)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C20" xr:uid="{B6689D0A-8653-4223-B9D9-AB23C60D1176}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3CD126-792B-4AA7-9A40-DBED65F3A336}">
+  <dimension ref="A1:U76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="L1" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+    </row>
+    <row r="2" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="11">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11">
+        <v>3</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="N4" s="11">
+        <v>2</v>
+      </c>
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="P4" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="11">
+        <v>2</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2</v>
+      </c>
+      <c r="G5" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="N5" s="11">
+        <v>3</v>
+      </c>
+      <c r="O5" s="11">
+        <v>3</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U5" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4</v>
+      </c>
+      <c r="D6" s="11">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>6</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="11">
+        <v>1</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>2</v>
+      </c>
+      <c r="R6" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U6" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="11">
+        <v>3</v>
+      </c>
+      <c r="O7" s="11">
+        <v>3</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>2</v>
+      </c>
+      <c r="G8" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="11">
+        <v>4</v>
+      </c>
+      <c r="O8" s="11">
+        <v>3</v>
+      </c>
+      <c r="P8" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>6</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U8" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>5</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="11">
+        <v>2</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>2</v>
+      </c>
+      <c r="S9" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U9" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="11">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="11">
+        <v>3</v>
+      </c>
+      <c r="O10" s="11">
+        <v>3</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>0</v>
+      </c>
+      <c r="R10" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="S10" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U10" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T13" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="11">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11">
+        <v>2</v>
+      </c>
+      <c r="E14" s="11">
+        <v>2</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
+        <v>5</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="11">
+        <v>2</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N14" s="11">
+        <v>3</v>
+      </c>
+      <c r="O14" s="11">
+        <v>3</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>0</v>
+      </c>
+      <c r="R14" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="S14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U14" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="11">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11">
+        <v>3</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <v>4</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="N15" s="11">
+        <v>1</v>
+      </c>
+      <c r="O15" s="11">
+        <v>0</v>
+      </c>
+      <c r="P15" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2</v>
+      </c>
+      <c r="R15" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="11">
+        <v>4</v>
+      </c>
+      <c r="D16" s="11">
+        <v>3</v>
+      </c>
+      <c r="E16" s="11">
+        <v>2</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="11">
+        <v>2</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="N16" s="11">
+        <v>4</v>
+      </c>
+      <c r="O16" s="11">
+        <v>3</v>
+      </c>
+      <c r="P16" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>0</v>
+      </c>
+      <c r="R16" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="S16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U16" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="11">
+        <v>3</v>
+      </c>
+      <c r="D17" s="11">
+        <v>3</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="11">
+        <v>2</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="N17" s="11">
+        <v>3</v>
+      </c>
+      <c r="O17" s="11">
+        <v>3</v>
+      </c>
+      <c r="P17" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="11">
+        <v>0</v>
+      </c>
+      <c r="R17" s="11">
+        <v>6</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U17" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="11">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11">
+        <v>2</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="11">
+        <v>2</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="11">
+        <v>2</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
+        <v>0</v>
+      </c>
+      <c r="R18" s="11">
+        <v>2</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U18" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11">
+        <v>2</v>
+      </c>
+      <c r="G19" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="11">
+        <v>2</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="N19" s="11">
+        <v>2</v>
+      </c>
+      <c r="O19" s="11">
+        <v>2</v>
+      </c>
+      <c r="P19" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>0</v>
+      </c>
+      <c r="R19" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U19" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="11">
+        <v>2</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="11">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>0</v>
+      </c>
+      <c r="R20" s="11">
+        <v>1</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U20" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="11">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11">
+        <v>3</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0</v>
+      </c>
+      <c r="G21" s="11">
+        <v>5</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="11">
+        <v>2</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="N21" s="11">
+        <v>2</v>
+      </c>
+      <c r="O21" s="11">
+        <v>1</v>
+      </c>
+      <c r="P21" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0</v>
+      </c>
+      <c r="R21" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U21" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="11">
+        <v>4</v>
+      </c>
+      <c r="D25" s="11">
+        <v>4</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="11">
+        <v>3</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="N25" s="11">
+        <v>2</v>
+      </c>
+      <c r="O25" s="11">
+        <v>2</v>
+      </c>
+      <c r="P25" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>0</v>
+      </c>
+      <c r="R25" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U25" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="11">
+        <v>3</v>
+      </c>
+      <c r="D26" s="11">
+        <v>3</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11">
+        <v>5</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="11">
+        <v>3</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="N26" s="11">
+        <v>3</v>
+      </c>
+      <c r="O26" s="11">
+        <v>3</v>
+      </c>
+      <c r="P26" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="11">
+        <v>0</v>
+      </c>
+      <c r="R26" s="11">
+        <v>5</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U26" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="11">
+        <v>4</v>
+      </c>
+      <c r="D27" s="11">
+        <v>4</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11">
+        <v>6</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="11">
+        <v>3</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" s="11">
+        <v>3</v>
+      </c>
+      <c r="O27" s="11">
+        <v>3</v>
+      </c>
+      <c r="P27" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="11">
+        <v>0</v>
+      </c>
+      <c r="R27" s="11">
+        <v>5</v>
+      </c>
+      <c r="S27" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U27" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11">
+        <v>2</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11">
+        <v>0</v>
+      </c>
+      <c r="G28" s="11">
+        <v>2</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="11">
+        <v>3</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="N28" s="11">
+        <v>3</v>
+      </c>
+      <c r="O28" s="11">
+        <v>3</v>
+      </c>
+      <c r="P28" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>0</v>
+      </c>
+      <c r="R28" s="11">
+        <v>5</v>
+      </c>
+      <c r="S28" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U28" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="11">
+        <v>3</v>
+      </c>
+      <c r="D29" s="11">
+        <v>3</v>
+      </c>
+      <c r="E29" s="11">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11">
+        <v>6</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="11">
+        <v>3</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="N29" s="11">
+        <v>3</v>
+      </c>
+      <c r="O29" s="11">
+        <v>3</v>
+      </c>
+      <c r="P29" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>0</v>
+      </c>
+      <c r="R29" s="11">
+        <v>5</v>
+      </c>
+      <c r="S29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U29" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="11">
+        <v>3</v>
+      </c>
+      <c r="D30" s="11">
+        <v>3</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <v>6</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" s="11">
+        <v>3</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="N30" s="11">
+        <v>3</v>
+      </c>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="18">
+        <v>38812</v>
+      </c>
+      <c r="S30" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U30" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="11"/>
+      <c r="M31" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="N31" s="11">
+        <v>3</v>
+      </c>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="S31" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U31" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="11">
+        <v>3</v>
+      </c>
+      <c r="D34" s="11">
+        <v>3</v>
+      </c>
+      <c r="E34" s="11">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11">
+        <v>0</v>
+      </c>
+      <c r="G34" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="11">
+        <v>4</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R34" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T34" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U34" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="11">
+        <v>3</v>
+      </c>
+      <c r="D35" s="11">
+        <v>3</v>
+      </c>
+      <c r="E35" s="11">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+      <c r="G35" s="11">
+        <v>5</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" s="11">
+        <v>4</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="N35" s="11">
+        <v>3</v>
+      </c>
+      <c r="O35" s="11">
+        <v>3</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="11">
+        <v>0</v>
+      </c>
+      <c r="R35" s="11">
+        <v>6</v>
+      </c>
+      <c r="S35" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T35" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U35" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0</v>
+      </c>
+      <c r="D36" s="11">
+        <v>2</v>
+      </c>
+      <c r="E36" s="11">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11">
+        <v>0</v>
+      </c>
+      <c r="G36" s="11">
+        <v>2</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="11">
+        <v>4</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="N36" s="11">
+        <v>4</v>
+      </c>
+      <c r="O36" s="11">
+        <v>4</v>
+      </c>
+      <c r="P36" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="11">
+        <v>0</v>
+      </c>
+      <c r="R36" s="11">
+        <v>6</v>
+      </c>
+      <c r="S36" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U36" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="11">
+        <v>3</v>
+      </c>
+      <c r="D37" s="11">
+        <v>3</v>
+      </c>
+      <c r="E37" s="11">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11">
+        <v>0</v>
+      </c>
+      <c r="G37" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" s="11">
+        <v>4</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="N37" s="11">
+        <v>4</v>
+      </c>
+      <c r="O37" s="11">
+        <v>4</v>
+      </c>
+      <c r="P37" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="11">
+        <v>0</v>
+      </c>
+      <c r="R37" s="11">
+        <v>6</v>
+      </c>
+      <c r="S37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U37" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="11">
+        <v>4</v>
+      </c>
+      <c r="D38" s="11">
+        <v>4</v>
+      </c>
+      <c r="E38" s="11">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11">
+        <v>0</v>
+      </c>
+      <c r="G38" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J38" s="11">
+        <v>4</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="N38" s="11">
+        <v>4</v>
+      </c>
+      <c r="O38" s="11">
+        <v>4</v>
+      </c>
+      <c r="P38" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="11">
+        <v>0</v>
+      </c>
+      <c r="R38" s="11">
+        <v>6</v>
+      </c>
+      <c r="S38" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T38" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U38" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="11">
+        <v>2</v>
+      </c>
+      <c r="D39" s="11">
+        <v>2</v>
+      </c>
+      <c r="E39" s="11">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11">
+        <v>0</v>
+      </c>
+      <c r="G39" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J39" s="11">
+        <v>4</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="N39" s="11">
+        <v>1</v>
+      </c>
+      <c r="O39" s="11">
+        <v>0</v>
+      </c>
+      <c r="P39" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="11">
+        <v>2</v>
+      </c>
+      <c r="R39" s="11">
+        <v>2</v>
+      </c>
+      <c r="S39" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T39" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U39" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="11">
+        <v>3</v>
+      </c>
+      <c r="D40" s="11">
+        <v>3</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11">
+        <v>0</v>
+      </c>
+      <c r="G40" s="11">
+        <v>5</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="11">
+        <v>4</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N40" s="11">
+        <v>3</v>
+      </c>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="S40" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T40" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U40" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q43" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S43" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U43" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="11">
+        <v>3</v>
+      </c>
+      <c r="D44" s="11">
+        <v>3</v>
+      </c>
+      <c r="E44" s="11">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11">
+        <v>0</v>
+      </c>
+      <c r="G44" s="11">
+        <v>5</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J44" s="11">
+        <v>5</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="N44" s="11">
+        <v>3</v>
+      </c>
+      <c r="O44" s="11">
+        <v>3</v>
+      </c>
+      <c r="P44" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>0</v>
+      </c>
+      <c r="R44" s="11">
+        <v>6</v>
+      </c>
+      <c r="S44" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T44" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U44" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="11">
+        <v>3</v>
+      </c>
+      <c r="D45" s="11">
+        <v>3</v>
+      </c>
+      <c r="E45" s="11">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11">
+        <v>0</v>
+      </c>
+      <c r="G45" s="11">
+        <v>5</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45" s="11">
+        <v>5</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="N45" s="11">
+        <v>3</v>
+      </c>
+      <c r="O45" s="11">
+        <v>3</v>
+      </c>
+      <c r="P45" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="11">
+        <v>0</v>
+      </c>
+      <c r="R45" s="11">
+        <v>6</v>
+      </c>
+      <c r="S45" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T45" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U45" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="11">
+        <v>2</v>
+      </c>
+      <c r="D46" s="11">
+        <v>1</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11">
+        <v>2</v>
+      </c>
+      <c r="G46" s="11">
+        <v>2</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J46" s="11">
+        <v>5</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="N46" s="11">
+        <v>3</v>
+      </c>
+      <c r="O46" s="11">
+        <v>3</v>
+      </c>
+      <c r="P46" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="11">
+        <v>0</v>
+      </c>
+      <c r="R46" s="11">
+        <v>6</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T46" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U46" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="11">
+        <v>3</v>
+      </c>
+      <c r="D47" s="11">
+        <v>3</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11">
+        <v>5</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J47" s="11">
+        <v>5</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="N47" s="11">
+        <v>1</v>
+      </c>
+      <c r="O47" s="11">
+        <v>0</v>
+      </c>
+      <c r="P47" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11">
+        <v>2</v>
+      </c>
+      <c r="R47" s="11">
+        <v>3</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T47" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U47" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C48" s="11">
+        <v>3</v>
+      </c>
+      <c r="D48" s="11">
+        <v>3</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11">
+        <v>0</v>
+      </c>
+      <c r="G48" s="11">
+        <v>4</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J48" s="11">
+        <v>5</v>
+      </c>
+      <c r="L48" s="11"/>
+      <c r="M48" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="N48" s="11">
+        <v>3</v>
+      </c>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11">
+        <v>6</v>
+      </c>
+      <c r="S48" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T48" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U48" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11"/>
+      <c r="B49" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" s="11">
+        <v>3</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="12">
+        <v>45387</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" s="11">
+        <v>5</v>
+      </c>
+      <c r="L49" s="11"/>
+      <c r="M49" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="N49" s="11">
+        <v>3</v>
+      </c>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11"/>
+      <c r="R49" s="11">
+        <v>6</v>
+      </c>
+      <c r="S49" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T49" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U49" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11"/>
+      <c r="B50" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C50" s="11">
+        <v>3</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J50" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L51" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P52" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q52" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S52" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U52" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="N53" s="11">
+        <v>1</v>
+      </c>
+      <c r="O53" s="11">
+        <v>0</v>
+      </c>
+      <c r="P53" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>2</v>
+      </c>
+      <c r="R53" s="11">
+        <v>3</v>
+      </c>
+      <c r="S53" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T53" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U53" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="11">
+        <v>3</v>
+      </c>
+      <c r="D54" s="11">
+        <v>3</v>
+      </c>
+      <c r="E54" s="11">
+        <v>0</v>
+      </c>
+      <c r="F54" s="11">
+        <v>0</v>
+      </c>
+      <c r="G54" s="11">
+        <v>5</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J54" s="11">
+        <v>6</v>
+      </c>
+      <c r="L54" s="11"/>
+      <c r="M54" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="N54" s="11">
+        <v>3</v>
+      </c>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11">
+        <v>6</v>
+      </c>
+      <c r="S54" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T54" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U54" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" s="11">
+        <v>1</v>
+      </c>
+      <c r="D55" s="11">
+        <v>0</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0</v>
+      </c>
+      <c r="F55" s="11">
+        <v>2</v>
+      </c>
+      <c r="G55" s="11">
+        <v>5</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J55" s="11">
+        <v>6</v>
+      </c>
+      <c r="L55" s="11"/>
+      <c r="M55" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="N55" s="11">
+        <v>3</v>
+      </c>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
+      <c r="R55" s="11">
+        <v>6</v>
+      </c>
+      <c r="S55" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T55" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U55" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" s="11">
+        <v>3</v>
+      </c>
+      <c r="D56" s="11">
+        <v>3</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0</v>
+      </c>
+      <c r="F56" s="11">
+        <v>0</v>
+      </c>
+      <c r="G56" s="11">
+        <v>6</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J56" s="11">
+        <v>6</v>
+      </c>
+      <c r="L56" s="11"/>
+      <c r="M56" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N56" s="11">
+        <v>3</v>
+      </c>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11">
+        <v>6</v>
+      </c>
+      <c r="S56" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T56" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U56" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C57" s="11">
+        <v>2</v>
+      </c>
+      <c r="D57" s="11">
+        <v>2</v>
+      </c>
+      <c r="E57" s="11">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11">
+        <v>0</v>
+      </c>
+      <c r="G57" s="11">
+        <v>4</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J57" s="11">
+        <v>6</v>
+      </c>
+      <c r="L57" s="11"/>
+      <c r="M57" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="N57" s="11">
+        <v>3</v>
+      </c>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+      <c r="R57" s="11">
+        <v>6</v>
+      </c>
+      <c r="S57" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T57" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U57" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" s="11">
+        <v>3</v>
+      </c>
+      <c r="D58" s="11">
+        <v>3</v>
+      </c>
+      <c r="E58" s="11">
+        <v>0</v>
+      </c>
+      <c r="F58" s="11">
+        <v>0</v>
+      </c>
+      <c r="G58" s="11">
+        <v>5</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J58" s="11">
+        <v>6</v>
+      </c>
+      <c r="L58" s="11"/>
+      <c r="M58" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="N58" s="11">
+        <v>3</v>
+      </c>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+      <c r="R58" s="11">
+        <v>4</v>
+      </c>
+      <c r="S58" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T58" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U58" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11"/>
+      <c r="B59" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J59" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L60" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O61" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P61" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q61" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R61" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S61" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T61" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U61" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="N62" s="11">
+        <v>0</v>
+      </c>
+      <c r="O62" s="11">
+        <v>2</v>
+      </c>
+      <c r="P62" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="11">
+        <v>0</v>
+      </c>
+      <c r="R62" s="11">
+        <v>2</v>
+      </c>
+      <c r="S62" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T62" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U62" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="11">
+        <v>0</v>
+      </c>
+      <c r="D63" s="11">
+        <v>2</v>
+      </c>
+      <c r="E63" s="11">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11">
+        <v>0</v>
+      </c>
+      <c r="G63" s="11">
+        <v>2</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J63" s="11">
+        <v>7</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="N63" s="11">
+        <v>4</v>
+      </c>
+      <c r="O63" s="11">
+        <v>1</v>
+      </c>
+      <c r="P63" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q63" s="11">
+        <v>0</v>
+      </c>
+      <c r="R63" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="S63" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T63" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U63" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="11">
+        <v>4</v>
+      </c>
+      <c r="D64" s="11">
+        <v>1</v>
+      </c>
+      <c r="E64" s="11">
+        <v>6</v>
+      </c>
+      <c r="F64" s="11">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11">
+        <v>8</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J64" s="11">
+        <v>7</v>
+      </c>
+      <c r="L64" s="11"/>
+      <c r="M64" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="N64" s="11">
+        <v>3</v>
+      </c>
+      <c r="O64" s="11"/>
+      <c r="P64" s="11"/>
+      <c r="Q64" s="11"/>
+      <c r="R64" s="11">
+        <v>6</v>
+      </c>
+      <c r="S64" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T64" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U64" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" s="11">
+        <v>3</v>
+      </c>
+      <c r="D65" s="11">
+        <v>3</v>
+      </c>
+      <c r="E65" s="11">
+        <v>0</v>
+      </c>
+      <c r="F65" s="11">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11">
+        <v>5</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J65" s="11">
+        <v>7</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="N65" s="11">
+        <v>3</v>
+      </c>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="11">
+        <v>6</v>
+      </c>
+      <c r="S65" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T65" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U65" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C66" s="11">
+        <v>3</v>
+      </c>
+      <c r="D66" s="11">
+        <v>2</v>
+      </c>
+      <c r="E66" s="11">
+        <v>2</v>
+      </c>
+      <c r="F66" s="11">
+        <v>0</v>
+      </c>
+      <c r="G66" s="11">
+        <v>7</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J66" s="11">
+        <v>7</v>
+      </c>
+      <c r="L66" s="11"/>
+      <c r="M66" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="N66" s="11">
+        <v>3</v>
+      </c>
+      <c r="O66" s="11"/>
+      <c r="P66" s="11"/>
+      <c r="Q66" s="11"/>
+      <c r="R66" s="11">
+        <v>6</v>
+      </c>
+      <c r="S66" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T66" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U66" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11"/>
+      <c r="B67" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J67" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="59.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11"/>
+      <c r="B68" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J68" s="11">
+        <v>7</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L69" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N69" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O69" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P69" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q69" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="R69" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="S69" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T69" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="U69" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="M70" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="N70" s="15">
+        <v>0</v>
+      </c>
+      <c r="O70" s="15">
+        <v>2</v>
+      </c>
+      <c r="P70" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="15">
+        <v>0</v>
+      </c>
+      <c r="R70" s="15">
+        <v>2</v>
+      </c>
+      <c r="S70" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="T70" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="U70" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="N71" s="11">
+        <v>4</v>
+      </c>
+      <c r="O71" s="11">
+        <v>1</v>
+      </c>
+      <c r="P71" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q71" s="11">
+        <v>0</v>
+      </c>
+      <c r="R71" s="11">
+        <v>12</v>
+      </c>
+      <c r="S71" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T71" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U71" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="15">
+        <v>0</v>
+      </c>
+      <c r="D72" s="15">
+        <v>2</v>
+      </c>
+      <c r="E72" s="15">
+        <v>0</v>
+      </c>
+      <c r="F72" s="15">
+        <v>0</v>
+      </c>
+      <c r="G72" s="15">
+        <v>2</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J72" s="15">
+        <v>8</v>
+      </c>
+      <c r="L72" s="11"/>
+      <c r="M72" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="N72" s="11">
+        <v>3</v>
+      </c>
+      <c r="O72" s="11"/>
+      <c r="P72" s="11"/>
+      <c r="Q72" s="11"/>
+      <c r="R72" s="11">
+        <v>4</v>
+      </c>
+      <c r="S72" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="T72" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U72" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="11">
+        <v>4</v>
+      </c>
+      <c r="D73" s="11">
+        <v>1</v>
+      </c>
+      <c r="E73" s="11">
+        <v>6</v>
+      </c>
+      <c r="F73" s="11">
+        <v>0</v>
+      </c>
+      <c r="G73" s="11">
+        <v>8</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J73" s="11">
+        <v>8</v>
+      </c>
+      <c r="L73" s="11"/>
+      <c r="M73" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="N73" s="11">
+        <v>3</v>
+      </c>
+      <c r="O73" s="11"/>
+      <c r="P73" s="11"/>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11">
+        <v>6</v>
+      </c>
+      <c r="S73" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T73" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U73" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="11">
+        <v>3</v>
+      </c>
+      <c r="D74" s="11">
+        <v>2</v>
+      </c>
+      <c r="E74" s="11">
+        <v>2</v>
+      </c>
+      <c r="F74" s="11">
+        <v>0</v>
+      </c>
+      <c r="G74" s="11">
+        <v>9</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="J74" s="11">
+        <v>8</v>
+      </c>
+      <c r="L74" s="11"/>
+      <c r="M74" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="N74" s="11">
+        <v>3</v>
+      </c>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11"/>
+      <c r="R74" s="11">
+        <v>6</v>
+      </c>
+      <c r="S74" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T74" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="U74" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11"/>
+      <c r="B75" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="11">
+        <v>3</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="12">
+        <v>45387</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J75" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11"/>
+      <c r="B76" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J76" s="11">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="L1:O1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=KIM&amp;numb=101E" xr:uid="{0697674C-1A27-4EF5-9CC9-3F66DA51DD67}"/>
+    <hyperlink ref="A5" r:id="rId2" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=BIL&amp;numb=110E" xr:uid="{1D8CE670-7DD0-4521-B50D-6D0A8C284B54}"/>
+    <hyperlink ref="A6" r:id="rId3" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=103E" xr:uid="{D488216C-AC0E-44A2-913D-E927462EF8A9}"/>
+    <hyperlink ref="A7" r:id="rId4" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=101E" xr:uid="{9E961C2A-2CCB-4D9F-9713-FD23857C70B2}"/>
+    <hyperlink ref="A8" r:id="rId5" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=101EL" xr:uid="{C44F3450-6BFE-4D30-B870-CB432CD09D4C}"/>
+    <hyperlink ref="A9" r:id="rId6" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=112E" xr:uid="{5445A42C-A1E4-4586-BDE9-DBCBA98C3748}"/>
+    <hyperlink ref="A10" r:id="rId7" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=100" xr:uid="{95E9B080-8237-4F2D-ABDD-EB5A98D99E67}"/>
+    <hyperlink ref="A14" r:id="rId8" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=106E" xr:uid="{680DC75D-F840-4ED4-9239-82BA635B2CD8}"/>
+    <hyperlink ref="A15" r:id="rId9" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=STA&amp;numb=201E" xr:uid="{3E108CD8-3FF2-48A9-B060-09C5574C279F}"/>
+    <hyperlink ref="A16" r:id="rId10" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=104E" xr:uid="{34032F4A-509D-4450-AEB2-645D43786E85}"/>
+    <hyperlink ref="A17" r:id="rId11" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=102E" xr:uid="{1C1DA2FC-53AC-4070-9236-AD11EE71D861}"/>
+    <hyperlink ref="A18" r:id="rId12" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=112A" xr:uid="{569A27DE-D782-4DDA-8676-0638E1113F07}"/>
+    <hyperlink ref="A19" r:id="rId13" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=102EL" xr:uid="{BB265E2A-997C-49FD-B4CC-605D2575B273}"/>
+    <hyperlink ref="A20" r:id="rId14" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=DAN&amp;numb=102" xr:uid="{E8BEC5F0-D753-4DBF-B568-5CA4542BB499}"/>
+    <hyperlink ref="A21" r:id="rId15" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=261E" xr:uid="{1E82689D-CAFA-4EB8-AFA5-A8F51D2EF70F}"/>
+    <hyperlink ref="A25" r:id="rId16" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=201E" xr:uid="{1A1314D7-0D32-42A6-9CCA-5064A8282C2E}"/>
+    <hyperlink ref="A26" r:id="rId17" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=DNK&amp;numb=201E" xr:uid="{A7C13E43-103E-44E9-B977-84193D7A0E9A}"/>
+    <hyperlink ref="A27" r:id="rId18" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MUK&amp;numb=211E" xr:uid="{CA9CF5F5-3434-4BAB-B34E-D89DCF04D8D9}"/>
+    <hyperlink ref="A28" r:id="rId19" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=TUR&amp;numb=121" xr:uid="{4B6F4B55-AA35-48C8-A84F-A7F0A2C2D00F}"/>
+    <hyperlink ref="A29" r:id="rId20" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=217E" xr:uid="{C3F76100-A9EB-45B9-9C37-A6500970E566}"/>
+    <hyperlink ref="A30" r:id="rId21" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=207E" xr:uid="{75CF87BD-CB9E-4413-B0DE-75B96ED1156A}"/>
+    <hyperlink ref="A34" r:id="rId22" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=AKM&amp;numb=219E" xr:uid="{FF46F75C-A657-4542-BDB9-67DBD5ACE1C2}"/>
+    <hyperlink ref="A35" r:id="rId23" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=202E" xr:uid="{0270AD2D-A6D6-43E9-B39B-FE7A011EA10D}"/>
+    <hyperlink ref="A36" r:id="rId24" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=TUR&amp;numb=122" xr:uid="{09B06E09-3A8A-4528-8B67-EAE453981403}"/>
+    <hyperlink ref="A37" r:id="rId25" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=203E" xr:uid="{7D40D4F7-E786-48E0-A10E-0CB7F0849B82}"/>
+    <hyperlink ref="A38" r:id="rId26" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=337E" xr:uid="{8D53D4C0-12DE-44C8-8EB9-5FF036EA2FE7}"/>
+    <hyperlink ref="A39" r:id="rId27" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=201A" xr:uid="{70BA6A33-D454-4DAE-AF10-29FDF4ED4386}"/>
+    <hyperlink ref="A40" r:id="rId28" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=220E" xr:uid="{243D3495-CB2F-48C5-A6A8-C3F55969C618}"/>
+    <hyperlink ref="A44" r:id="rId29" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=305E" xr:uid="{FCFD4CD1-50A7-4B23-B3A9-A8E8C9C81858}"/>
+    <hyperlink ref="A45" r:id="rId30" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=352E" xr:uid="{0D09EAB8-17C7-4879-B181-93BB91919D33}"/>
+    <hyperlink ref="A46" r:id="rId31" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=301E" xr:uid="{0C765878-AE66-4F2F-AF35-F55509DA7DA2}"/>
+    <hyperlink ref="A47" r:id="rId32" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=303E" xr:uid="{16FAB73A-6FCB-428E-BD51-E664B5769636}"/>
+    <hyperlink ref="A48" r:id="rId33" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=411E" xr:uid="{5520F238-8F6A-49CC-8E6B-E8A2521B9932}"/>
+    <hyperlink ref="B49" r:id="rId34" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221051.html" xr:uid="{06BCEBDE-7279-4199-A16E-25C475C253C1}"/>
+    <hyperlink ref="B50" r:id="rId35" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221052.html" xr:uid="{2EC2D890-AA57-4978-A64B-9D58FCA4A769}"/>
+    <hyperlink ref="A54" r:id="rId36" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=310E" xr:uid="{826EAFA0-F1FD-4537-8822-44FBD6F184AC}"/>
+    <hyperlink ref="A55" r:id="rId37" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UCK&amp;numb=304E" xr:uid="{891783E7-F059-49A0-9FD7-1B42895D83A7}"/>
+    <hyperlink ref="A56" r:id="rId38" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=421E" xr:uid="{2F16A795-178F-4759-A3D6-A3D21190E530}"/>
+    <hyperlink ref="A57" r:id="rId39" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=314E" xr:uid="{75ADFB7B-308D-42FB-9225-D879844051A3}"/>
+    <hyperlink ref="A58" r:id="rId40" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=451E" xr:uid="{B7A0628E-9D4A-420D-8749-1029A72A2096}"/>
+    <hyperlink ref="B59" r:id="rId41" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221061.html" xr:uid="{B8F0B7C3-222A-4643-86EB-69E111CF859C}"/>
+    <hyperlink ref="A63" r:id="rId42" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ATA&amp;numb=121" xr:uid="{B34FA3B2-C1DF-4751-B612-9E2555A849C3}"/>
+    <hyperlink ref="A64" r:id="rId43" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=4901E" xr:uid="{A2F3E9B5-767D-4AA1-A500-DC8660BE191D}"/>
+    <hyperlink ref="A65" r:id="rId44" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=441E" xr:uid="{66B46EA3-2D4B-4320-9ED4-7C2ED6EFD200}"/>
+    <hyperlink ref="A66" r:id="rId45" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=419E" xr:uid="{38065DB3-E3D1-4AE8-AEC3-5943FBD3109B}"/>
+    <hyperlink ref="B67" r:id="rId46" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221071.html" xr:uid="{238D5328-9DE3-4246-AEFE-65E5E7186015}"/>
+    <hyperlink ref="B68" r:id="rId47" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221072.html" xr:uid="{7D81B9C6-73B4-4D3F-9E2C-475375ACB3E6}"/>
+    <hyperlink ref="A72" r:id="rId48" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ATA&amp;numb=122" xr:uid="{2D07DEA4-29BB-4856-990D-D7BA0C07ED89}"/>
+    <hyperlink ref="A73" r:id="rId49" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=4902E" xr:uid="{F2DF2D70-8752-43DF-96AE-02B28EEF3C02}"/>
+    <hyperlink ref="A74" r:id="rId50" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=UZB&amp;numb=420E" xr:uid="{80C2C8EC-C2DE-4AB3-A313-7590B8BC1664}"/>
+    <hyperlink ref="B75" r:id="rId51" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221081.html" xr:uid="{CF9F938E-104E-4025-A04C-E1742F6AB723}"/>
+    <hyperlink ref="B76" r:id="rId52" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/UZBE/20221082.html" xr:uid="{D5699C0E-9E4D-4326-BF97-66DA8A498B42}"/>
+    <hyperlink ref="L4" r:id="rId53" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=101E" xr:uid="{F421AF86-BE18-4BFD-AE88-58DBCB5C316A}"/>
+    <hyperlink ref="L5" r:id="rId54" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=101E" xr:uid="{7E023888-6C82-4561-8933-898B4CEAEE73}"/>
+    <hyperlink ref="L6" r:id="rId55" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=101EL" xr:uid="{D893F900-96E0-4E3C-831B-374C3D69F3DE}"/>
+    <hyperlink ref="L7" r:id="rId56" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=KIM&amp;numb=101E" xr:uid="{B80A8B7F-5999-4537-B34E-3E31108EDE8A}"/>
+    <hyperlink ref="L8" r:id="rId57" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=103E" xr:uid="{111E3778-9D60-4B36-A00C-1883D2E0966F}"/>
+    <hyperlink ref="L9" r:id="rId58" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=TUR&amp;numb=121" xr:uid="{14E30730-C7A3-454D-97EA-8B167E65B770}"/>
+    <hyperlink ref="L10" r:id="rId59" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=100" xr:uid="{3EDAB416-E0A3-4935-80AB-FFE0111DDFA9}"/>
+    <hyperlink ref="L14" r:id="rId60" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=102E" xr:uid="{215C4A71-585F-46C8-9EA4-2E625E63559A}"/>
+    <hyperlink ref="L15" r:id="rId61" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=FIZ&amp;numb=102EL" xr:uid="{F39F1E38-AF68-4F5A-AB56-84534773DA90}"/>
+    <hyperlink ref="L16" r:id="rId62" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=MAT&amp;numb=104E" xr:uid="{300CEF3B-58E2-4CAE-8CFD-DA9251461FD8}"/>
+    <hyperlink ref="L17" r:id="rId63" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=281E" xr:uid="{0D2D82E6-E7D0-4B15-8CE1-2115A07C6519}"/>
+    <hyperlink ref="L18" r:id="rId64" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=TUR&amp;numb=122" xr:uid="{760438D6-6FC3-4AC4-B60F-6DF460DD83FA}"/>
+    <hyperlink ref="L19" r:id="rId65" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=112A" xr:uid="{4FDBCE3E-63C6-4DAD-A3B9-BA0EF5D446B0}"/>
+    <hyperlink ref="L20" r:id="rId66" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=DAN&amp;numb=102" xr:uid="{6906599D-B5F7-4569-BB6E-F4404C6C2FEC}"/>
+    <hyperlink ref="L21" r:id="rId67" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=110E" xr:uid="{94DCA741-98AB-4E28-BCC8-CB857549332A}"/>
+    <hyperlink ref="L25" r:id="rId68" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ING&amp;numb=201A" xr:uid="{65225AB9-948A-4F41-87E1-FD453318B2B2}"/>
+    <hyperlink ref="L26" r:id="rId69" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=211E" xr:uid="{D0003369-BAA1-4324-9BD1-13E1C6CCAF1C}"/>
+    <hyperlink ref="L27" r:id="rId70" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=210E" xr:uid="{18FEC4B7-CB36-4CB3-B8E0-164FBAA1DE7F}"/>
+    <hyperlink ref="L28" r:id="rId71" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=205E" xr:uid="{309E54F2-2F1D-40EB-8EF4-2B2F3D66E856}"/>
+    <hyperlink ref="L29" r:id="rId72" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=271E" xr:uid="{C17001C3-1DF7-4F4B-91F7-B8127F9E8B53}"/>
+    <hyperlink ref="M30" r:id="rId73" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221031.html" xr:uid="{56448438-ECA5-484E-A234-8D3B8720690F}"/>
+    <hyperlink ref="M31" r:id="rId74" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221032.html" xr:uid="{2A333210-65A4-42B6-AC05-A601A09FFF4A}"/>
+    <hyperlink ref="L35" r:id="rId75" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=232E" xr:uid="{975BADA7-2ADA-4793-95AD-610B41F75188}"/>
+    <hyperlink ref="L36" r:id="rId76" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=212E" xr:uid="{4BCF837A-B1E9-419E-BC87-9DE48A31661E}"/>
+    <hyperlink ref="L37" r:id="rId77" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=262E" xr:uid="{49FFADF2-8D1E-4BED-8102-927412FC0255}"/>
+    <hyperlink ref="L38" r:id="rId78" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=206E" xr:uid="{C62F695B-7243-40E2-BAD0-27A55C3F25FC}"/>
+    <hyperlink ref="L39" r:id="rId79" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=221E" xr:uid="{A2DE8932-8659-4B2C-95F8-A8D380F0A4A0}"/>
+    <hyperlink ref="M40" r:id="rId80" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221041.html" xr:uid="{2FE21FC9-0033-4E72-A7D4-9BF245CF23FB}"/>
+    <hyperlink ref="L44" r:id="rId81" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EEF&amp;numb=311E" xr:uid="{BA110046-B81A-4436-94B3-7E91702EE720}"/>
+    <hyperlink ref="L45" r:id="rId82" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=KON&amp;numb=313E" xr:uid="{BFA9E075-13E6-45EF-85E6-E5771FFB5E74}"/>
+    <hyperlink ref="L46" r:id="rId83" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=307E" xr:uid="{A68649FB-C2BF-4A1A-A5E7-08CC19672135}"/>
+    <hyperlink ref="L47" r:id="rId84" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=324E" xr:uid="{4B5558CD-9313-4701-A41C-3FEE4B88EDC6}"/>
+    <hyperlink ref="M48" r:id="rId85" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221051.html" xr:uid="{91D9890F-ECB6-4964-85EE-0C01705136B4}"/>
+    <hyperlink ref="M49" r:id="rId86" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221052.html" xr:uid="{00C0D943-FAC9-462F-A7EF-B0F839253D65}"/>
+    <hyperlink ref="L53" r:id="rId87" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=311E" xr:uid="{DDD0B27A-102B-4B47-875E-E78616996692}"/>
+    <hyperlink ref="M54" r:id="rId88" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221061.html" xr:uid="{DCFAC4B6-9F1F-4B1A-BAF6-4511D83F3250}"/>
+    <hyperlink ref="M55" r:id="rId89" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221062.html" xr:uid="{4DCF4D03-B727-41D8-AD45-AC06BCE7B092}"/>
+    <hyperlink ref="M56" r:id="rId90" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221063.html" xr:uid="{C1C9DCDF-57DB-4DB0-A87D-47A9E3E21537}"/>
+    <hyperlink ref="M57" r:id="rId91" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221064.html" xr:uid="{D8144F62-0897-43FD-A04C-639C94171D96}"/>
+    <hyperlink ref="M58" r:id="rId92" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221065.html" xr:uid="{9F8A2830-ED38-484B-B214-C75C47279F56}"/>
+    <hyperlink ref="L62" r:id="rId93" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ATA&amp;numb=121" xr:uid="{CF472F0C-C257-40A7-AC24-90BBA679A880}"/>
+    <hyperlink ref="L63" r:id="rId94" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=4901E" xr:uid="{E43E9C48-6024-461D-BAA8-8728279A9BB7}"/>
+    <hyperlink ref="M64" r:id="rId95" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221071.html" xr:uid="{9425B957-DE2E-47CA-A27F-008DD0FA4614}"/>
+    <hyperlink ref="M65" r:id="rId96" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221072.html" xr:uid="{C560EA4E-144A-49EA-9D21-BA596FCEE3EF}"/>
+    <hyperlink ref="M66" r:id="rId97" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221073.html" xr:uid="{A4BC18C0-AAAC-4053-A528-713F2B2A876D}"/>
+    <hyperlink ref="L70" r:id="rId98" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=ATA&amp;numb=122" xr:uid="{28840629-4FEE-4477-ABE8-EE80FACCA2EA}"/>
+    <hyperlink ref="L71" r:id="rId99" tooltip="Click For Course Catalogue Form." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-information/course-information.php?subj=EHB&amp;numb=4902E" xr:uid="{956174B9-739D-4957-A83C-F5F3E9E8E4A1}"/>
+    <hyperlink ref="M72" r:id="rId100" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221081.html" xr:uid="{A34F42B5-E322-4225-8BB5-C1CE7D107B25}"/>
+    <hyperlink ref="M73" r:id="rId101" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221082.html" xr:uid="{F938BC7F-74AC-4974-8EB7-46C05BF4CF8C}"/>
+    <hyperlink ref="M74" r:id="rId102" tooltip="Ders Listesini Görmek İçin Tıklayınız." display="https://www.sis.itu.edu.tr/EN/student/undergraduate/course-plans/plans/EHBE/20221083.html" xr:uid="{FF0151A1-DE29-45C9-A337-6BBDBA5FB522}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId103"/>
+</worksheet>
 </file>